--- a/data/clean_field_data.xlsx
+++ b/data/clean_field_data.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>Stemming</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Ch_length</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>TQ</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>SD_TQ</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Stemming</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Ch_length</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
@@ -625,22 +625,22 @@
         <v>6.75</v>
       </c>
       <c r="O2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q2" t="n">
         <v>35</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>3500</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="S2" t="n">
         <v>67.61234037828133</v>
       </c>
-      <c r="R2" t="n">
+      <c r="T2" t="n">
         <v>6.761234037828133</v>
-      </c>
-      <c r="S2" t="n">
-        <v>4</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2</v>
       </c>
       <c r="U2" t="n">
         <v>1.57401796720284</v>
@@ -722,22 +722,22 @@
         <v>7.875</v>
       </c>
       <c r="O3" t="n">
+        <v>4</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q3" t="n">
         <v>35</v>
       </c>
-      <c r="P3" t="n">
+      <c r="R3" t="n">
         <v>3500</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
         <v>72.68326590665242</v>
       </c>
-      <c r="R3" t="n">
+      <c r="T3" t="n">
         <v>7.268326590665243</v>
-      </c>
-      <c r="S3" t="n">
-        <v>4</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2</v>
       </c>
       <c r="U3" t="n">
         <v>1.66392609771817</v>
@@ -819,22 +819,22 @@
         <v>9.125</v>
       </c>
       <c r="O4" t="n">
+        <v>4</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q4" t="n">
         <v>35</v>
       </c>
-      <c r="P4" t="n">
+      <c r="R4" t="n">
         <v>3500</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="S4" t="n">
         <v>81.13480845393759</v>
       </c>
-      <c r="R4" t="n">
+      <c r="T4" t="n">
         <v>8.113480845393759</v>
-      </c>
-      <c r="S4" t="n">
-        <v>4</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2</v>
       </c>
       <c r="U4" t="n">
         <v>2.586259144048288</v>
@@ -916,22 +916,22 @@
         <v>27</v>
       </c>
       <c r="O5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="n">
         <v>35</v>
       </c>
-      <c r="P5" t="n">
+      <c r="R5" t="n">
         <v>1575</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="S5" t="n">
         <v>52.39956379316803</v>
       </c>
-      <c r="R5" t="n">
+      <c r="T5" t="n">
         <v>7.81126577552403</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
       </c>
       <c r="U5" t="n">
         <v>2.176795086935746</v>
@@ -1013,22 +1013,22 @@
         <v>10.63</v>
       </c>
       <c r="O6" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="Q6" t="n">
         <v>35</v>
       </c>
-      <c r="P6" t="n">
+      <c r="R6" t="n">
         <v>1575</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
         <v>54.08987230262506</v>
       </c>
-      <c r="R6" t="n">
+      <c r="T6" t="n">
         <v>8.063242090863515</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.333333333333333</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.666666666666667</v>
       </c>
       <c r="U6" t="n">
         <v>2.853015971352396</v>
@@ -1110,22 +1110,22 @@
         <v>6.25</v>
       </c>
       <c r="O7" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="Q7" t="n">
         <v>35</v>
       </c>
-      <c r="P7" t="n">
+      <c r="R7" t="n">
         <v>1575</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="S7" t="n">
         <v>76.06388292556649</v>
       </c>
-      <c r="R7" t="n">
+      <c r="T7" t="n">
         <v>11.33893419027682</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.333333333333333</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.666666666666667</v>
       </c>
       <c r="U7" t="n">
         <v>1.264973825883335</v>
@@ -1207,22 +1207,22 @@
         <v>24.63</v>
       </c>
       <c r="O8" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="Q8" t="n">
         <v>35</v>
       </c>
-      <c r="P8" t="n">
+      <c r="R8" t="n">
         <v>1575</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="S8" t="n">
         <v>30.4255531702266</v>
       </c>
-      <c r="R8" t="n">
+      <c r="T8" t="n">
         <v>4.535573676110727</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.333333333333333</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.666666666666667</v>
       </c>
       <c r="U8" t="n">
         <v>1.979621206397625</v>
@@ -1304,22 +1304,22 @@
         <v>28.88</v>
       </c>
       <c r="O9" t="n">
+        <v>4</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q9" t="n">
         <v>90</v>
       </c>
-      <c r="P9" t="n">
+      <c r="R9" t="n">
         <v>6300</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="S9" t="n">
         <v>26.3523138347365</v>
       </c>
-      <c r="R9" t="n">
+      <c r="T9" t="n">
         <v>3.14970394174356</v>
-      </c>
-      <c r="S9" t="n">
-        <v>4</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2</v>
       </c>
       <c r="U9" t="n">
         <v>0.6976370858327973</v>
@@ -1401,22 +1401,22 @@
         <v>14.25</v>
       </c>
       <c r="O10" t="n">
+        <v>4</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q10" t="n">
         <v>90</v>
       </c>
-      <c r="P10" t="n">
+      <c r="R10" t="n">
         <v>6300</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="S10" t="n">
         <v>29.51459149490487</v>
       </c>
-      <c r="R10" t="n">
+      <c r="T10" t="n">
         <v>3.527668414752787</v>
-      </c>
-      <c r="S10" t="n">
-        <v>4</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2</v>
       </c>
       <c r="U10" t="n">
         <v>1.464643327530867</v>
@@ -1498,22 +1498,22 @@
         <v>8.125</v>
       </c>
       <c r="O11" t="n">
+        <v>4</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="n">
         <v>90</v>
       </c>
-      <c r="P11" t="n">
+      <c r="R11" t="n">
         <v>6300</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="S11" t="n">
         <v>31.62277660168379</v>
       </c>
-      <c r="R11" t="n">
+      <c r="T11" t="n">
         <v>3.779644730092272</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2</v>
       </c>
       <c r="U11" t="n">
         <v>1.084513364288608</v>
@@ -1595,22 +1595,22 @@
         <v>28.75</v>
       </c>
       <c r="O12" t="n">
+        <v>4</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="n">
         <v>90</v>
       </c>
-      <c r="P12" t="n">
+      <c r="R12" t="n">
         <v>6300</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="S12" t="n">
         <v>45.32597979574677</v>
       </c>
-      <c r="R12" t="n">
+      <c r="T12" t="n">
         <v>5.417490779798924</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2</v>
       </c>
       <c r="U12" t="n">
         <v>1.155307632344655</v>
@@ -1692,22 +1692,22 @@
         <v>6.5</v>
       </c>
       <c r="O13" t="n">
+        <v>4</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="n">
         <v>25</v>
       </c>
-      <c r="P13" t="n">
+      <c r="R13" t="n">
         <v>2500</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="S13" t="n">
         <v>90</v>
       </c>
-      <c r="R13" t="n">
+      <c r="T13" t="n">
         <v>9</v>
-      </c>
-      <c r="S13" t="n">
-        <v>4</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
       </c>
       <c r="U13" t="n">
         <v>0.4928652983889979</v>
@@ -1789,22 +1789,22 @@
         <v>6</v>
       </c>
       <c r="O14" t="n">
+        <v>4</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q14" t="n">
         <v>25</v>
       </c>
-      <c r="P14" t="n">
+      <c r="R14" t="n">
         <v>2500</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="S14" t="n">
         <v>86</v>
       </c>
-      <c r="R14" t="n">
+      <c r="T14" t="n">
         <v>8.6</v>
-      </c>
-      <c r="S14" t="n">
-        <v>4</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
       </c>
       <c r="U14" t="n">
         <v>1.332629836534198</v>
@@ -1886,22 +1886,22 @@
         <v>6.25</v>
       </c>
       <c r="O15" t="n">
+        <v>4</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" t="n">
         <v>25</v>
       </c>
-      <c r="P15" t="n">
+      <c r="R15" t="n">
         <v>2500</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="S15" t="n">
         <v>90</v>
       </c>
-      <c r="R15" t="n">
+      <c r="T15" t="n">
         <v>9</v>
-      </c>
-      <c r="S15" t="n">
-        <v>4</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
       </c>
       <c r="U15" t="n">
         <v>1.322555520152884</v>
@@ -1983,22 +1983,22 @@
         <v>10.63</v>
       </c>
       <c r="O16" t="n">
+        <v>4</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
         <v>25</v>
       </c>
-      <c r="P16" t="n">
+      <c r="R16" t="n">
         <v>2500</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="S16" t="n">
         <v>80</v>
       </c>
-      <c r="R16" t="n">
+      <c r="T16" t="n">
         <v>8</v>
-      </c>
-      <c r="S16" t="n">
-        <v>4</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
       </c>
       <c r="U16" t="n">
         <v>1.203272559211543</v>
@@ -2080,22 +2080,22 @@
         <v>5.75</v>
       </c>
       <c r="O17" t="n">
+        <v>3</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q17" t="n">
         <v>33</v>
       </c>
-      <c r="P17" t="n">
+      <c r="R17" t="n">
         <v>2970</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="S17" t="n">
         <v>78.33494518006403</v>
       </c>
-      <c r="R17" t="n">
+      <c r="T17" t="n">
         <v>8.257228238447704</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.5</v>
       </c>
       <c r="U17" t="n">
         <v>0.6037693694087286</v>
@@ -2177,22 +2177,22 @@
         <v>19.88</v>
       </c>
       <c r="O18" t="n">
+        <v>3</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q18" t="n">
         <v>33</v>
       </c>
-      <c r="P18" t="n">
+      <c r="R18" t="n">
         <v>2970</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="S18" t="n">
         <v>81.81649829917798</v>
       </c>
-      <c r="R18" t="n">
+      <c r="T18" t="n">
         <v>8.624216160156491</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.5</v>
       </c>
       <c r="U18" t="n">
         <v>0.4548899914356874</v>
@@ -2274,22 +2274,22 @@
         <v>7.625</v>
       </c>
       <c r="O19" t="n">
+        <v>3</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q19" t="n">
         <v>33</v>
       </c>
-      <c r="P19" t="n">
+      <c r="R19" t="n">
         <v>2970</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="S19" t="n">
         <v>73.11261550139309</v>
       </c>
-      <c r="R19" t="n">
+      <c r="T19" t="n">
         <v>7.706746355884524</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.5</v>
       </c>
       <c r="U19" t="n">
         <v>0.6010318916521397</v>
@@ -2371,22 +2371,22 @@
         <v>5.75</v>
       </c>
       <c r="O20" t="n">
+        <v>3</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q20" t="n">
         <v>33</v>
       </c>
-      <c r="P20" t="n">
+      <c r="R20" t="n">
         <v>2970</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="S20" t="n">
         <v>74.85339206095007</v>
       </c>
-      <c r="R20" t="n">
+      <c r="T20" t="n">
         <v>7.890240316738917</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.5</v>
       </c>
       <c r="U20" t="n">
         <v>0.6749832099322741</v>
@@ -2468,22 +2468,22 @@
         <v>5.75</v>
       </c>
       <c r="O21" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="Q21" t="n">
         <v>43</v>
       </c>
-      <c r="P21" t="n">
+      <c r="R21" t="n">
         <v>3440</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="S21" t="n">
         <v>77.77427086962838</v>
       </c>
-      <c r="R21" t="n">
+      <c r="T21" t="n">
         <v>8.695427828248537</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.333333333333333</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.666666666666667</v>
       </c>
       <c r="U21" t="n">
         <v>0.6825916666204287</v>
@@ -2565,22 +2565,22 @@
         <v>5.375</v>
       </c>
       <c r="O22" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="Q22" t="n">
         <v>43</v>
       </c>
-      <c r="P22" t="n">
+      <c r="R22" t="n">
         <v>3440</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="S22" t="n">
         <v>73.19931375965024</v>
       </c>
-      <c r="R22" t="n">
+      <c r="T22" t="n">
         <v>8.183932073645682</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.333333333333333</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.666666666666667</v>
       </c>
       <c r="U22" t="n">
         <v>0.8372475245337022</v>
@@ -2662,22 +2662,22 @@
         <v>3</v>
       </c>
       <c r="O23" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="Q23" t="n">
         <v>43</v>
       </c>
-      <c r="P23" t="n">
+      <c r="R23" t="n">
         <v>3440</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="S23" t="n">
         <v>70.14934235299815</v>
       </c>
-      <c r="R23" t="n">
+      <c r="T23" t="n">
         <v>7.842934903910446</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.333333333333333</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.666666666666667</v>
       </c>
       <c r="U23" t="n">
         <v>1.096610285997437</v>
@@ -2759,22 +2759,22 @@
         <v>2.75</v>
       </c>
       <c r="O24" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="Q24" t="n">
         <v>43</v>
       </c>
-      <c r="P24" t="n">
+      <c r="R24" t="n">
         <v>3440</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="S24" t="n">
         <v>65.57438524302</v>
       </c>
-      <c r="R24" t="n">
+      <c r="T24" t="n">
         <v>7.33143914930759</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.333333333333333</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.666666666666667</v>
       </c>
       <c r="U24" t="n">
         <v>1.621564092231941</v>
@@ -2856,22 +2856,22 @@
         <v>2.75</v>
       </c>
       <c r="O25" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="Q25" t="n">
         <v>43</v>
       </c>
-      <c r="P25" t="n">
+      <c r="R25" t="n">
         <v>3440</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="S25" t="n">
         <v>64.04939953969397</v>
       </c>
-      <c r="R25" t="n">
+      <c r="T25" t="n">
         <v>7.160940564439972</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.333333333333333</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.666666666666667</v>
       </c>
       <c r="U25" t="n">
         <v>1.998367051902165</v>
@@ -2953,22 +2953,22 @@
         <v>5.375</v>
       </c>
       <c r="O26" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="Q26" t="n">
         <v>50</v>
       </c>
-      <c r="P26" t="n">
+      <c r="R26" t="n">
         <v>5200</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="S26" t="n">
         <v>65.05382386916237</v>
       </c>
-      <c r="R26" t="n">
+      <c r="T26" t="n">
         <v>6.379052256590135</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.666666666666667</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1.333333333333333</v>
       </c>
       <c r="U26" t="n">
         <v>0.5265021031509983</v>
@@ -3050,22 +3050,22 @@
         <v>3.375</v>
       </c>
       <c r="O27" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="Q27" t="n">
         <v>50</v>
       </c>
-      <c r="P27" t="n">
+      <c r="R27" t="n">
         <v>5200</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="S27" t="n">
         <v>67.88225099390856</v>
       </c>
-      <c r="R27" t="n">
+      <c r="T27" t="n">
         <v>6.65640235470275</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.666666666666667</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1.333333333333333</v>
       </c>
       <c r="U27" t="n">
         <v>0.3030631744900834</v>
@@ -3147,22 +3147,22 @@
         <v>8.375</v>
       </c>
       <c r="O28" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="Q28" t="n">
         <v>50</v>
       </c>
-      <c r="P28" t="n">
+      <c r="R28" t="n">
         <v>5200</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="S28" t="n">
         <v>67.88225099390856</v>
       </c>
-      <c r="R28" t="n">
+      <c r="T28" t="n">
         <v>6.65640235470275</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.666666666666667</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1.333333333333333</v>
       </c>
       <c r="U28" t="n">
         <v>0.3400373027857091</v>
@@ -3244,22 +3244,22 @@
         <v>4.75</v>
       </c>
       <c r="O29" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="Q29" t="n">
         <v>50</v>
       </c>
-      <c r="P29" t="n">
+      <c r="R29" t="n">
         <v>5200</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="S29" t="n">
         <v>66.46803743153546</v>
       </c>
-      <c r="R29" t="n">
+      <c r="T29" t="n">
         <v>6.517727305646442</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.666666666666667</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1.333333333333333</v>
       </c>
       <c r="U29" t="n">
         <v>0.5247285289349821</v>
@@ -3341,22 +3341,22 @@
         <v>5.125</v>
       </c>
       <c r="O30" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="Q30" t="n">
         <v>50</v>
       </c>
-      <c r="P30" t="n">
+      <c r="R30" t="n">
         <v>5200</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="S30" t="n">
         <v>63.63961030678927</v>
       </c>
-      <c r="R30" t="n">
+      <c r="T30" t="n">
         <v>6.240377207533828</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.666666666666667</v>
-      </c>
-      <c r="T30" t="n">
-        <v>1.333333333333333</v>
       </c>
       <c r="U30" t="n">
         <v>0.5855619698800079</v>
@@ -3438,22 +3438,22 @@
         <v>4.125</v>
       </c>
       <c r="O31" t="n">
+        <v>4</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q31" t="n">
         <v>45</v>
       </c>
-      <c r="P31" t="n">
+      <c r="R31" t="n">
         <v>2700</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="S31" t="n">
         <v>71.55417527999327</v>
       </c>
-      <c r="R31" t="n">
+      <c r="T31" t="n">
         <v>9.237604307034012</v>
-      </c>
-      <c r="S31" t="n">
-        <v>4</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2</v>
       </c>
       <c r="U31" t="n">
         <v>1.213130742110702</v>
@@ -3535,22 +3535,22 @@
         <v>4.875</v>
       </c>
       <c r="O32" t="n">
+        <v>4</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q32" t="n">
         <v>45</v>
       </c>
-      <c r="P32" t="n">
+      <c r="R32" t="n">
         <v>2700</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="S32" t="n">
         <v>74.53559924999298</v>
       </c>
-      <c r="R32" t="n">
+      <c r="T32" t="n">
         <v>9.622504486493762</v>
-      </c>
-      <c r="S32" t="n">
-        <v>4</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2</v>
       </c>
       <c r="U32" t="n">
         <v>1.311840175194943</v>
@@ -3632,22 +3632,22 @@
         <v>5</v>
       </c>
       <c r="O33" t="n">
+        <v>4</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q33" t="n">
         <v>45</v>
       </c>
-      <c r="P33" t="n">
+      <c r="R33" t="n">
         <v>2700</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="S33" t="n">
         <v>76.02631123499285</v>
       </c>
-      <c r="R33" t="n">
+      <c r="T33" t="n">
         <v>9.814954576223638</v>
-      </c>
-      <c r="S33" t="n">
-        <v>4</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2</v>
       </c>
       <c r="U33" t="n">
         <v>1.124280035416687</v>
@@ -3729,22 +3729,22 @@
         <v>7.125</v>
       </c>
       <c r="O34" t="n">
+        <v>4</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q34" t="n">
         <v>45</v>
       </c>
-      <c r="P34" t="n">
+      <c r="R34" t="n">
         <v>2700</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="S34" t="n">
         <v>73.04488726499312</v>
       </c>
-      <c r="R34" t="n">
+      <c r="T34" t="n">
         <v>9.430054396763888</v>
-      </c>
-      <c r="S34" t="n">
-        <v>4</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2</v>
       </c>
       <c r="U34" t="n">
         <v>1.338153985791956</v>
@@ -3826,22 +3826,22 @@
         <v>5</v>
       </c>
       <c r="O35" t="n">
+        <v>4</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q35" t="n">
         <v>45</v>
       </c>
-      <c r="P35" t="n">
+      <c r="R35" t="n">
         <v>2700</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="S35" t="n">
         <v>70.06346329499341</v>
       </c>
-      <c r="R35" t="n">
+      <c r="T35" t="n">
         <v>9.045154217304137</v>
-      </c>
-      <c r="S35" t="n">
-        <v>4</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2</v>
       </c>
       <c r="U35" t="n">
         <v>1.476591999100671</v>
@@ -3923,22 +3923,22 @@
         <v>5.625</v>
       </c>
       <c r="O36" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="Q36" t="n">
         <v>25</v>
       </c>
-      <c r="P36" t="n">
+      <c r="R36" t="n">
         <v>3000</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="S36" t="n">
         <v>76</v>
       </c>
-      <c r="R36" t="n">
+      <c r="T36" t="n">
         <v>6.937819061732104</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2.333333333333333</v>
-      </c>
-      <c r="T36" t="n">
-        <v>1.166666666666667</v>
       </c>
       <c r="U36" t="n">
         <v>1.748677979525604</v>
@@ -4020,22 +4020,22 @@
         <v>7.75</v>
       </c>
       <c r="O37" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="Q37" t="n">
         <v>25</v>
       </c>
-      <c r="P37" t="n">
+      <c r="R37" t="n">
         <v>3000</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="S37" t="n">
         <v>84</v>
       </c>
-      <c r="R37" t="n">
+      <c r="T37" t="n">
         <v>7.668115805072325</v>
-      </c>
-      <c r="S37" t="n">
-        <v>2.333333333333333</v>
-      </c>
-      <c r="T37" t="n">
-        <v>1.166666666666667</v>
       </c>
       <c r="U37" t="n">
         <v>1.522135584031304</v>
@@ -4117,22 +4117,22 @@
         <v>7.625</v>
       </c>
       <c r="O38" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="Q38" t="n">
         <v>25</v>
       </c>
-      <c r="P38" t="n">
+      <c r="R38" t="n">
         <v>3000</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="S38" t="n">
         <v>88</v>
       </c>
-      <c r="R38" t="n">
+      <c r="T38" t="n">
         <v>8.033264176742437</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.333333333333333</v>
-      </c>
-      <c r="T38" t="n">
-        <v>1.166666666666667</v>
       </c>
       <c r="U38" t="n">
         <v>1.957415140669637</v>
@@ -4214,22 +4214,22 @@
         <v>9.875</v>
       </c>
       <c r="O39" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="Q39" t="n">
         <v>25</v>
       </c>
-      <c r="P39" t="n">
+      <c r="R39" t="n">
         <v>3000</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="S39" t="n">
         <v>94</v>
       </c>
-      <c r="R39" t="n">
+      <c r="T39" t="n">
         <v>8.580986734247602</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.333333333333333</v>
-      </c>
-      <c r="T39" t="n">
-        <v>1.166666666666667</v>
       </c>
       <c r="U39" t="n">
         <v>1.633154439051417</v>
@@ -4311,22 +4311,22 @@
         <v>8</v>
       </c>
       <c r="O40" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="Q40" t="n">
         <v>25</v>
       </c>
-      <c r="P40" t="n">
+      <c r="R40" t="n">
         <v>3000</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="S40" t="n">
         <v>80</v>
       </c>
-      <c r="R40" t="n">
+      <c r="T40" t="n">
         <v>7.302967433402214</v>
-      </c>
-      <c r="S40" t="n">
-        <v>2.333333333333333</v>
-      </c>
-      <c r="T40" t="n">
-        <v>1.166666666666667</v>
       </c>
       <c r="U40" t="n">
         <v>1.19543647330365</v>
@@ -4408,22 +4408,22 @@
         <v>5.875</v>
       </c>
       <c r="O41" t="n">
+        <v>4</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q41" t="n">
         <v>35</v>
       </c>
-      <c r="P41" t="n">
+      <c r="R41" t="n">
         <v>5600</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="S41" t="n">
         <v>81.13480845393759</v>
       </c>
-      <c r="R41" t="n">
+      <c r="T41" t="n">
         <v>6.414269805898185</v>
-      </c>
-      <c r="S41" t="n">
-        <v>4</v>
-      </c>
-      <c r="T41" t="n">
-        <v>2</v>
       </c>
       <c r="U41" t="n">
         <v>0.5799784824543073</v>
@@ -4505,22 +4505,22 @@
         <v>5.5</v>
       </c>
       <c r="O42" t="n">
+        <v>4</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q42" t="n">
         <v>35</v>
       </c>
-      <c r="P42" t="n">
+      <c r="R42" t="n">
         <v>5600</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="S42" t="n">
         <v>82.82511696339462</v>
       </c>
-      <c r="R42" t="n">
+      <c r="T42" t="n">
         <v>6.547900426854397</v>
-      </c>
-      <c r="S42" t="n">
-        <v>4</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2</v>
       </c>
       <c r="U42" t="n">
         <v>0.4074631107708374</v>
@@ -4602,22 +4602,22 @@
         <v>8.5</v>
       </c>
       <c r="O43" t="n">
+        <v>4</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q43" t="n">
         <v>35</v>
       </c>
-      <c r="P43" t="n">
+      <c r="R43" t="n">
         <v>5600</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="S43" t="n">
         <v>87.89604249176573</v>
       </c>
-      <c r="R43" t="n">
+      <c r="T43" t="n">
         <v>6.948792289723033</v>
-      </c>
-      <c r="S43" t="n">
-        <v>4</v>
-      </c>
-      <c r="T43" t="n">
-        <v>2</v>
       </c>
       <c r="U43" t="n">
         <v>0.5647454657554211</v>
@@ -4699,22 +4699,22 @@
         <v>6.25</v>
       </c>
       <c r="O44" t="n">
+        <v>4</v>
+      </c>
+      <c r="P44" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q44" t="n">
         <v>35</v>
       </c>
-      <c r="P44" t="n">
+      <c r="R44" t="n">
         <v>5600</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="S44" t="n">
         <v>91.27665951067979</v>
       </c>
-      <c r="R44" t="n">
+      <c r="T44" t="n">
         <v>7.216053531635458</v>
-      </c>
-      <c r="S44" t="n">
-        <v>4</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2</v>
       </c>
       <c r="U44" t="n">
         <v>0.5704144151776482</v>
@@ -4796,22 +4796,22 @@
         <v>5.375</v>
       </c>
       <c r="O45" t="n">
+        <v>4</v>
+      </c>
+      <c r="P45" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q45" t="n">
         <v>35</v>
       </c>
-      <c r="P45" t="n">
+      <c r="R45" t="n">
         <v>5600</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="S45" t="n">
         <v>84.51542547285166</v>
       </c>
-      <c r="R45" t="n">
+      <c r="T45" t="n">
         <v>6.681531047810609</v>
-      </c>
-      <c r="S45" t="n">
-        <v>4</v>
-      </c>
-      <c r="T45" t="n">
-        <v>2</v>
       </c>
       <c r="U45" t="n">
         <v>0.946625931670228</v>
